--- a/research/traditional_assets/database/data/philippines/philippines_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08130000000000001</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0557</v>
+        <v>0.112</v>
       </c>
       <c r="F2">
-        <v>0.2325</v>
+        <v>0.229</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3041.6</v>
+        <v>3295.6</v>
       </c>
       <c r="L2">
-        <v>0.2777006792783581</v>
+        <v>0.3012706828777768</v>
       </c>
       <c r="M2">
-        <v>799.2329999999999</v>
+        <v>473.1995</v>
       </c>
       <c r="N2">
-        <v>0.02383358332910875</v>
+        <v>0.01463020962156814</v>
       </c>
       <c r="O2">
-        <v>0.2627672935297212</v>
+        <v>0.1435852348585993</v>
       </c>
       <c r="P2">
-        <v>798.724</v>
+        <v>472.1755</v>
       </c>
       <c r="Q2">
-        <v>0.0238184046591658</v>
+        <v>0.01459854996289884</v>
       </c>
       <c r="R2">
-        <v>0.2625999473961073</v>
+        <v>0.1432745175385362</v>
       </c>
       <c r="S2">
-        <v>0.5089999999999755</v>
+        <v>1.023999999999993</v>
       </c>
       <c r="T2">
-        <v>0.0006368605900907189</v>
+        <v>0.002163992142848826</v>
       </c>
       <c r="U2">
-        <v>15119</v>
+        <v>11209.7</v>
       </c>
       <c r="V2">
-        <v>0.4508571922740868</v>
+        <v>0.3465774177590898</v>
       </c>
       <c r="W2">
-        <v>0.07275496756747506</v>
+        <v>0.09389561975768872</v>
       </c>
       <c r="X2">
-        <v>0.06562076383363948</v>
+        <v>0.1108490215241899</v>
       </c>
       <c r="Y2">
-        <v>0.007134203733835581</v>
+        <v>-0.01695340176650117</v>
       </c>
       <c r="Z2">
-        <v>0.2689972690126434</v>
+        <v>0.3028182471260987</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05078867807618516</v>
+        <v>0.08158214459267932</v>
       </c>
       <c r="AC2">
-        <v>-0.05078867807618516</v>
+        <v>-0.08158214459267932</v>
       </c>
       <c r="AD2">
-        <v>18000.2</v>
+        <v>19453.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18000.2</v>
+        <v>19453.5</v>
       </c>
       <c r="AG2">
-        <v>2881.200000000001</v>
+        <v>8243.799999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3492871710188011</v>
+        <v>0.3755683189343115</v>
       </c>
       <c r="AI2">
-        <v>0.343874235127127</v>
+        <v>0.3803322469583783</v>
       </c>
       <c r="AJ2">
-        <v>0.07912102397082529</v>
+        <v>0.2031102942263439</v>
       </c>
       <c r="AK2">
-        <v>0.07739689413129966</v>
+        <v>0.2064097749067328</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.005430000000000001</v>
+        <v>0.0224</v>
       </c>
       <c r="E3">
-        <v>-0.156</v>
+        <v>-0.0225</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>10.2</v>
+        <v>16.5</v>
       </c>
       <c r="L3">
-        <v>0.1536144578313253</v>
+        <v>0.2534562211981567</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>57.3</v>
+        <v>62.6</v>
       </c>
       <c r="V3">
-        <v>0.02500327267967012</v>
+        <v>0.02929066067752199</v>
       </c>
       <c r="W3">
-        <v>0.01846822379141771</v>
+        <v>0.03280318091451292</v>
       </c>
       <c r="X3">
-        <v>0.04986448861678964</v>
+        <v>0.07958488326285784</v>
       </c>
       <c r="Y3">
-        <v>-0.03139626482537193</v>
+        <v>-0.04678170234834492</v>
       </c>
       <c r="Z3">
-        <v>0.1360376971931981</v>
+        <v>0.1460623737940319</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04986448861678964</v>
+        <v>0.07958488326285784</v>
       </c>
       <c r="AC3">
-        <v>-0.04986448861678964</v>
+        <v>-0.07958488326285784</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-57.3</v>
+        <v>-62.6</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.02564446831364125</v>
+        <v>-0.03017449146823484</v>
       </c>
       <c r="AK3">
-        <v>-0.1285618128786179</v>
+        <v>-0.2266473569876901</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Security Bank Corporation (PSE:SECB)</t>
+          <t>BDO Unibank, Inc. (PSE:BDO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.08130000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E4">
-        <v>-0.07480000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="F4">
-        <v>0.227</v>
+        <v>0.173</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>109.7</v>
+        <v>857.6</v>
       </c>
       <c r="L4">
-        <v>0.1986599058312206</v>
+        <v>0.2608510508866381</v>
       </c>
       <c r="M4">
-        <v>29.3865</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="N4">
-        <v>0.01687424633936262</v>
+        <v>0.008665979525872851</v>
       </c>
       <c r="O4">
-        <v>0.2678805834092981</v>
+        <v>0.1009794776119403</v>
       </c>
       <c r="P4">
-        <v>29.3865</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>0.01687424633936262</v>
+        <v>0.008665979525872851</v>
       </c>
       <c r="R4">
-        <v>0.2678805834092981</v>
+        <v>0.1009794776119403</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1671.4</v>
+        <v>2885.9</v>
       </c>
       <c r="V4">
-        <v>0.9597473442434683</v>
+        <v>0.2887892645925689</v>
       </c>
       <c r="W4">
-        <v>0.04293206011271134</v>
+        <v>0.1053976993412644</v>
       </c>
       <c r="X4">
-        <v>0.05914859333450225</v>
+        <v>0.08912962585951779</v>
       </c>
       <c r="Y4">
-        <v>-0.01621653322179091</v>
+        <v>0.01626807348174658</v>
       </c>
       <c r="Z4">
-        <v>0.1651681293109121</v>
+        <v>0.3945681916374633</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05045838225387853</v>
+        <v>0.08052461958388121</v>
       </c>
       <c r="AC4">
-        <v>-0.05045838225387853</v>
+        <v>-0.08052461958388121</v>
       </c>
       <c r="AD4">
-        <v>664.4</v>
+        <v>3118.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>664.4</v>
+        <v>3118.2</v>
       </c>
       <c r="AG4">
-        <v>-1007</v>
+        <v>232.2999999999997</v>
       </c>
       <c r="AH4">
-        <v>0.2761544536348144</v>
+        <v>0.23782538726137</v>
       </c>
       <c r="AI4">
-        <v>0.2137640359061806</v>
+        <v>0.2916467914363478</v>
       </c>
       <c r="AJ4">
-        <v>-1.371000680735194</v>
+        <v>0.02271793768458933</v>
       </c>
       <c r="AK4">
-        <v>-0.7009118117909099</v>
+        <v>0.02975992210920082</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0975</v>
+        <v>-0.00106</v>
       </c>
       <c r="E5">
-        <v>0.134</v>
+        <v>-0.126</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,82 +975,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>111.2</v>
+        <v>41.7</v>
       </c>
       <c r="L5">
-        <v>0.2345991561181435</v>
+        <v>0.1223591549295775</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>15.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05677179962894249</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.3669064748201439</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>15.3</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05677179962894249</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.3669064748201439</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>947.5</v>
+        <v>250.1</v>
       </c>
       <c r="V5">
-        <v>2.258641239570918</v>
+        <v>0.9280148423005565</v>
       </c>
       <c r="W5">
-        <v>0.09777543304317243</v>
+        <v>0.03578477645241569</v>
       </c>
       <c r="X5">
-        <v>0.05945352074515371</v>
+        <v>0.09502109139944967</v>
       </c>
       <c r="Y5">
-        <v>0.03832191229801873</v>
+        <v>-0.05923631494703398</v>
       </c>
       <c r="Z5">
-        <v>0.6611800809038918</v>
+        <v>1.109375</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05047237457324477</v>
+        <v>0.08091012727303552</v>
       </c>
       <c r="AC5">
-        <v>-0.05047237457324477</v>
+        <v>-0.08091012727303552</v>
       </c>
       <c r="AD5">
-        <v>165.3</v>
+        <v>136</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>165.3</v>
+        <v>136</v>
       </c>
       <c r="AG5">
-        <v>-782.2</v>
+        <v>-114.1</v>
       </c>
       <c r="AH5">
-        <v>0.2826607387140903</v>
+        <v>0.3353884093711467</v>
       </c>
       <c r="AI5">
-        <v>0.1242296708251917</v>
+        <v>0.1179838639715451</v>
       </c>
       <c r="AJ5">
-        <v>2.156603253377447</v>
+        <v>-0.7342342342342342</v>
       </c>
       <c r="AK5">
-        <v>-2.041764552336205</v>
+        <v>-0.1264125858630623</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BDO Unibank, Inc. (PSE:BDO)</t>
+          <t>Bank of the Philippine Islands (PSE:BPI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1079,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.118</v>
+        <v>0.0852</v>
       </c>
       <c r="E6">
-        <v>0.105</v>
+        <v>0.112</v>
       </c>
       <c r="F6">
-        <v>0.238</v>
+        <v>0.226</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,28 +1100,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>862.8</v>
+        <v>629.4</v>
       </c>
       <c r="L6">
-        <v>0.2514352324056535</v>
+        <v>0.3592670814544209</v>
       </c>
       <c r="M6">
-        <v>103.1</v>
+        <v>150.7</v>
       </c>
       <c r="N6">
-        <v>0.01002898776288399</v>
+        <v>0.01822756026464433</v>
       </c>
       <c r="O6">
-        <v>0.1194946685210941</v>
+        <v>0.2394343819510645</v>
       </c>
       <c r="P6">
-        <v>103.1</v>
+        <v>150.7</v>
       </c>
       <c r="Q6">
-        <v>0.01002898776288399</v>
+        <v>0.01822756026464433</v>
       </c>
       <c r="R6">
-        <v>0.1194946685210941</v>
+        <v>0.2394343819510645</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3982.8</v>
+        <v>500.8</v>
       </c>
       <c r="V6">
-        <v>0.3874243691756969</v>
+        <v>0.06057307352709943</v>
       </c>
       <c r="W6">
-        <v>0.1125533219405925</v>
+        <v>0.110152435289382</v>
       </c>
       <c r="X6">
-        <v>0.05951692486790099</v>
+        <v>0.08577202360543895</v>
       </c>
       <c r="Y6">
-        <v>0.05303639707269151</v>
+        <v>0.02438041168394309</v>
       </c>
       <c r="Z6">
-        <v>0.4376243432127735</v>
+        <v>0.2466735190999846</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05047525249179863</v>
+        <v>0.08146098362522193</v>
       </c>
       <c r="AC6">
-        <v>-0.05047525249179863</v>
+        <v>-0.08146098362522193</v>
       </c>
       <c r="AD6">
-        <v>4077.6</v>
+        <v>1672.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4077.6</v>
+        <v>1672.3</v>
       </c>
       <c r="AG6">
-        <v>94.79999999999973</v>
+        <v>1171.5</v>
       </c>
       <c r="AH6">
-        <v>0.2839989413419883</v>
+        <v>0.1682394366197183</v>
       </c>
       <c r="AI6">
-        <v>0.3302449138266165</v>
+        <v>0.237397612253879</v>
       </c>
       <c r="AJ6">
-        <v>0.009137349397590335</v>
+        <v>0.1241100940757691</v>
       </c>
       <c r="AK6">
-        <v>0.01133374778824539</v>
+        <v>0.1790326277985787</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Metropolitan Bank &amp; Trust Company (PSE:MBT)</t>
+          <t>Union Bank of the Philippines (PSE:UBP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,13 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0446</v>
+        <v>0.135</v>
       </c>
       <c r="E7">
-        <v>0.0104</v>
-      </c>
-      <c r="F7">
-        <v>0.362</v>
+        <v>0.0732</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,85 +1222,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>370.2</v>
+        <v>201.5</v>
       </c>
       <c r="L7">
-        <v>0.2214644651830582</v>
+        <v>0.2798611111111111</v>
       </c>
       <c r="M7">
-        <v>351.852</v>
+        <v>73.639</v>
       </c>
       <c r="N7">
-        <v>0.07234245533236014</v>
+        <v>0.02223064150943396</v>
       </c>
       <c r="O7">
-        <v>0.9504376012965964</v>
+        <v>0.365454094292804</v>
       </c>
       <c r="P7">
-        <v>351.5</v>
+        <v>72.7</v>
       </c>
       <c r="Q7">
-        <v>0.07227008244751938</v>
+        <v>0.02194716981132076</v>
       </c>
       <c r="R7">
-        <v>0.9494867639113993</v>
+        <v>0.3607940446650124</v>
       </c>
       <c r="S7">
-        <v>0.3519999999999754</v>
+        <v>0.938999999999993</v>
       </c>
       <c r="T7">
-        <v>0.00100042063140177</v>
+        <v>0.01275139532041436</v>
       </c>
       <c r="U7">
-        <v>2742.5</v>
+        <v>747.7</v>
       </c>
       <c r="V7">
-        <v>0.5638711269198348</v>
+        <v>0.2257207547169811</v>
       </c>
       <c r="W7">
-        <v>0.05615386949003428</v>
+        <v>0.09389561975768872</v>
       </c>
       <c r="X7">
-        <v>0.06562076383363948</v>
+        <v>0.1091466900830964</v>
       </c>
       <c r="Y7">
-        <v>-0.009466894343605196</v>
+        <v>-0.01525107032540765</v>
       </c>
       <c r="Z7">
-        <v>0.2042871458949478</v>
+        <v>0.2803301666407101</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05070968721824128</v>
+        <v>0.08152684091429033</v>
       </c>
       <c r="AC7">
-        <v>-0.05070968721824128</v>
+        <v>-0.08152684091429033</v>
       </c>
       <c r="AD7">
-        <v>3149.1</v>
+        <v>3201.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3149.1</v>
+        <v>3201.3</v>
       </c>
       <c r="AG7">
-        <v>406.5999999999999</v>
+        <v>2453.6</v>
       </c>
       <c r="AH7">
-        <v>0.3930086861022364</v>
+        <v>0.4914642758451288</v>
       </c>
       <c r="AI7">
-        <v>0.3301531719488798</v>
+        <v>0.5633413694194661</v>
       </c>
       <c r="AJ7">
-        <v>0.07714930838851677</v>
+        <v>0.4255215830457328</v>
       </c>
       <c r="AK7">
-        <v>0.05983107213278789</v>
+        <v>0.4971833839918947</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Union Bank of the Philippines (PSE:UBP)</t>
+          <t>Security Bank Corporation (PSE:SECB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,10 +1326,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.104</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="E8">
-        <v>0.0557</v>
+        <v>0.0269</v>
+      </c>
+      <c r="F8">
+        <v>0.314</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,28 +1347,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>269</v>
+        <v>181.2</v>
       </c>
       <c r="L8">
-        <v>0.3447392028706908</v>
+        <v>0.296078431372549</v>
       </c>
       <c r="M8">
-        <v>84.7</v>
+        <v>38.4285</v>
       </c>
       <c r="N8">
-        <v>0.02875670537108712</v>
+        <v>0.03263844063190079</v>
       </c>
       <c r="O8">
-        <v>0.3148698884758365</v>
+        <v>0.2120778145695364</v>
       </c>
       <c r="P8">
-        <v>84.7</v>
+        <v>38.4285</v>
       </c>
       <c r="Q8">
-        <v>0.02875670537108712</v>
+        <v>0.03263844063190079</v>
       </c>
       <c r="R8">
-        <v>0.3148698884758365</v>
+        <v>0.2120778145695364</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1374,55 +1377,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1507</v>
+        <v>945</v>
       </c>
       <c r="V8">
-        <v>0.5116452773816799</v>
+        <v>0.802615933412604</v>
       </c>
       <c r="W8">
-        <v>0.127627271433316</v>
+        <v>0.07421059098169308</v>
       </c>
       <c r="X8">
-        <v>0.06820301012615283</v>
+        <v>0.1108490215241899</v>
       </c>
       <c r="Y8">
-        <v>0.05942426130716312</v>
+        <v>-0.03663843054249681</v>
       </c>
       <c r="Z8">
-        <v>0.2786785714285714</v>
+        <v>0.4309373591707977</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05078867807618516</v>
+        <v>0.08158214459267932</v>
       </c>
       <c r="AC8">
-        <v>-0.05078867807618516</v>
+        <v>-0.08158214459267932</v>
       </c>
       <c r="AD8">
-        <v>2219.6</v>
+        <v>1203.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2219.6</v>
+        <v>1203.4</v>
       </c>
       <c r="AG8">
-        <v>712.5999999999999</v>
+        <v>258.4000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.4297386253630203</v>
+        <v>0.5054603494623656</v>
       </c>
       <c r="AI8">
-        <v>0.5066538839051337</v>
+        <v>0.3623607347184583</v>
       </c>
       <c r="AJ8">
-        <v>0.194805904866047</v>
+        <v>0.1799693550633794</v>
       </c>
       <c r="AK8">
-        <v>0.2479557395873203</v>
+        <v>0.1087542087542088</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,7 +1442,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Philippine Bank of Communications (PSE:PBC)</t>
+          <t>Metropolitan Bank &amp; Trust Company (PSE:MBT)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1448,10 +1451,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0552</v>
+        <v>0.0568</v>
       </c>
       <c r="E9">
-        <v>0.311</v>
+        <v>0.09519999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.232</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1466,82 +1472,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>15.3</v>
+        <v>501.9</v>
       </c>
       <c r="L9">
-        <v>0.1863580998781973</v>
+        <v>0.2954612350621063</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.732</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.0001678706570347437</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.0014584578601315</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.647</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.0001483774796468295</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.001289101414624427</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.08499999999999996</v>
+      </c>
+      <c r="T9">
+        <v>0.1161202185792349</v>
       </c>
       <c r="U9">
-        <v>111.9</v>
+        <v>2540.6</v>
       </c>
       <c r="V9">
-        <v>0.662130177514793</v>
+        <v>0.5826396055498222</v>
       </c>
       <c r="W9">
-        <v>0.05799848369977256</v>
+        <v>0.08082255752910675</v>
       </c>
       <c r="X9">
-        <v>0.07284607836985317</v>
+        <v>0.1108834580227293</v>
       </c>
       <c r="Y9">
-        <v>-0.01484759467008061</v>
+        <v>-0.03006090049362257</v>
       </c>
       <c r="Z9">
-        <v>0.349808265871325</v>
+        <v>0.2607447657641063</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05090902109578926</v>
+        <v>0.08158323193629555</v>
       </c>
       <c r="AC9">
-        <v>-0.05090902109578926</v>
+        <v>-0.08158323193629555</v>
       </c>
       <c r="AD9">
-        <v>159.6</v>
+        <v>4461.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>159.6</v>
+        <v>4461.7</v>
       </c>
       <c r="AG9">
-        <v>47.69999999999999</v>
+        <v>1921.1</v>
       </c>
       <c r="AH9">
-        <v>0.4856968959220937</v>
+        <v>0.5057355308199768</v>
       </c>
       <c r="AI9">
-        <v>0.3775727466288147</v>
+        <v>0.4513560813749988</v>
       </c>
       <c r="AJ9">
-        <v>0.2201199815413013</v>
+        <v>0.3058297249108507</v>
       </c>
       <c r="AK9">
-        <v>0.1534749034749034</v>
+        <v>0.261569882224794</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1567,10 +1576,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="E10">
-        <v>0.172</v>
+        <v>0.206</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1585,28 +1594,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>293.4</v>
+        <v>316.8</v>
       </c>
       <c r="L10">
-        <v>0.3795601552393273</v>
+        <v>0.4155299055613851</v>
       </c>
       <c r="M10">
-        <v>52.6</v>
+        <v>68.8</v>
       </c>
       <c r="N10">
-        <v>0.03870493009565858</v>
+        <v>0.05185408501658124</v>
       </c>
       <c r="O10">
-        <v>0.1792774369461486</v>
+        <v>0.2171717171717172</v>
       </c>
       <c r="P10">
-        <v>52.6</v>
+        <v>68.8</v>
       </c>
       <c r="Q10">
-        <v>0.03870493009565858</v>
+        <v>0.05185408501658124</v>
       </c>
       <c r="R10">
-        <v>0.1792774369461486</v>
+        <v>0.2171717171717172</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1615,55 +1624,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1087.1</v>
+        <v>1296</v>
       </c>
       <c r="V10">
-        <v>0.7999264164827078</v>
+        <v>0.9767862526379258</v>
       </c>
       <c r="W10">
-        <v>0.1410983937674329</v>
+        <v>0.1420054686449415</v>
       </c>
       <c r="X10">
-        <v>0.07488903680617481</v>
+        <v>0.1265975456552416</v>
       </c>
       <c r="Y10">
-        <v>0.06620935696125807</v>
+        <v>0.0154079229896999</v>
       </c>
       <c r="Z10">
-        <v>0.3200563100364359</v>
+        <v>0.3019525525763396</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05095479973425201</v>
+        <v>0.08197871439629928</v>
       </c>
       <c r="AC10">
-        <v>-0.05095479973425201</v>
+        <v>-0.08197871439629928</v>
       </c>
       <c r="AD10">
-        <v>1397.5</v>
+        <v>2039.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1397.5</v>
+        <v>2039.2</v>
       </c>
       <c r="AG10">
-        <v>310.4000000000001</v>
+        <v>743.2</v>
       </c>
       <c r="AH10">
-        <v>0.5069834935606747</v>
+        <v>0.6058229352347</v>
       </c>
       <c r="AI10">
-        <v>0.3850817006971425</v>
+        <v>0.4746078294465391</v>
       </c>
       <c r="AJ10">
-        <v>0.1859350664909549</v>
+        <v>0.3590338164251208</v>
       </c>
       <c r="AK10">
-        <v>0.122108575924469</v>
+        <v>0.2476837965740185</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1680,7 +1689,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bank of the Philippine Islands (PSE:BPI)</t>
+          <t>Rizal Commercial Banking Corporation (PSE:RCB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1689,13 +1698,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0434</v>
+        <v>0.117</v>
       </c>
       <c r="E11">
-        <v>-0.00054</v>
-      </c>
-      <c r="F11">
-        <v>0.196</v>
+        <v>0.256</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1710,28 +1716,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>425.1</v>
+        <v>201</v>
       </c>
       <c r="L11">
-        <v>0.2728848375914752</v>
+        <v>0.3106646058732612</v>
       </c>
       <c r="M11">
-        <v>159.1</v>
+        <v>39</v>
       </c>
       <c r="N11">
-        <v>0.01969815151852815</v>
+        <v>0.04496713939813213</v>
       </c>
       <c r="O11">
-        <v>0.3742648788520348</v>
+        <v>0.1940298507462687</v>
       </c>
       <c r="P11">
-        <v>159.1</v>
+        <v>39</v>
       </c>
       <c r="Q11">
-        <v>0.01969815151852815</v>
+        <v>0.04496713939813213</v>
       </c>
       <c r="R11">
-        <v>0.3742648788520348</v>
+        <v>0.1940298507462687</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1740,55 +1746,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>559</v>
+        <v>777.4</v>
       </c>
       <c r="V11">
-        <v>0.06920972155158539</v>
+        <v>0.8963449786694339</v>
       </c>
       <c r="W11">
-        <v>0.07275496756747506</v>
+        <v>0.09368445583780005</v>
       </c>
       <c r="X11">
-        <v>0.05573126777268224</v>
+        <v>0.1508420418103137</v>
       </c>
       <c r="Y11">
-        <v>0.01702369979479282</v>
+        <v>-0.05715758597251366</v>
       </c>
       <c r="Z11">
-        <v>0.180570527755561</v>
+        <v>0.191498360720756</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05106463603586044</v>
+        <v>0.08234948825012406</v>
       </c>
       <c r="AC11">
-        <v>-0.05106463603586044</v>
+        <v>-0.08234948825012406</v>
       </c>
       <c r="AD11">
-        <v>1947.2</v>
+        <v>2020.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1947.2</v>
+        <v>2020.4</v>
       </c>
       <c r="AG11">
-        <v>1388.2</v>
+        <v>1243</v>
       </c>
       <c r="AH11">
-        <v>0.1942518530341876</v>
+        <v>0.6996571666031791</v>
       </c>
       <c r="AI11">
-        <v>0.252833863533078</v>
+        <v>0.5062897809853155</v>
       </c>
       <c r="AJ11">
-        <v>0.146665117114452</v>
+        <v>0.5890157797469554</v>
       </c>
       <c r="AK11">
-        <v>0.1943577178858943</v>
+        <v>0.3868417776671231</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1805,7 +1811,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rizal Commercial Banking Corporation (PSE:RCB)</t>
+          <t>Philippine National Bank (PSE:PNB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1814,10 +1820,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.06860000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="E12">
-        <v>0.04940000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1832,85 +1838,82 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>124.4</v>
+        <v>318.4</v>
       </c>
       <c r="L12">
-        <v>0.2162350078220059</v>
+        <v>0.3293679528292128</v>
       </c>
       <c r="M12">
-        <v>18.4945</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.02336934546373515</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.1486696141479099</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>18.3375</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.02317096285064443</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.1474075562700964</v>
+        <v>-0</v>
       </c>
       <c r="S12">
-        <v>0.157</v>
-      </c>
-      <c r="T12">
-        <v>0.00848901024628944</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>866.1</v>
+        <v>1165.5</v>
       </c>
       <c r="V12">
-        <v>1.094389689158453</v>
+        <v>2.238333013251392</v>
       </c>
       <c r="W12">
-        <v>0.06066812972445745</v>
+        <v>0.1077568701773386</v>
       </c>
       <c r="X12">
-        <v>0.1146690271964193</v>
+        <v>0.1590966071388105</v>
       </c>
       <c r="Y12">
-        <v>-0.05400089747196182</v>
+        <v>-0.05133973696147197</v>
       </c>
       <c r="Z12">
-        <v>0.2278793083369841</v>
+        <v>0.3003199850880735</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.05142796371929152</v>
+        <v>0.08243846375066191</v>
       </c>
       <c r="AC12">
-        <v>-0.05142796371929152</v>
+        <v>-0.08243846375066191</v>
       </c>
       <c r="AD12">
-        <v>2107.5</v>
+        <v>1353.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>2107.5</v>
+        <v>1353.5</v>
       </c>
       <c r="AG12">
-        <v>1241.4</v>
+        <v>188</v>
       </c>
       <c r="AH12">
-        <v>0.7269998965124702</v>
+        <v>0.7221747945790203</v>
       </c>
       <c r="AI12">
-        <v>0.4954859641698406</v>
+        <v>0.3188532120898019</v>
       </c>
       <c r="AJ12">
-        <v>0.6106847697756789</v>
+        <v>0.2652744461690419</v>
       </c>
       <c r="AK12">
-        <v>0.3664865822336374</v>
+        <v>0.0610508540624797</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1927,7 +1930,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Philippine National Bank (PSE:PNB)</t>
+          <t>Philippine Bank of Communications (PSE:PBC)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1936,10 +1939,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.12</v>
+        <v>0.0645</v>
       </c>
       <c r="E13">
-        <v>0.264</v>
+        <v>0.198</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1954,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>450.3</v>
+        <v>29.6</v>
       </c>
       <c r="L13">
-        <v>0.455492615820352</v>
+        <v>0.3414071510957324</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1981,55 +1984,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1586.4</v>
+        <v>38.1</v>
       </c>
       <c r="V13">
-        <v>2.663532572196105</v>
+        <v>0.3423180592991914</v>
       </c>
       <c r="W13">
-        <v>0.1424188753241824</v>
+        <v>0.1125047510452299</v>
       </c>
       <c r="X13">
-        <v>0.1361733435997891</v>
+        <v>0.1476054938259125</v>
       </c>
       <c r="Y13">
-        <v>0.006245531724393294</v>
+        <v>-0.03510074278068259</v>
       </c>
       <c r="Z13">
-        <v>0.2789896994496966</v>
+        <v>0.2789575289575289</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05406359442077587</v>
+        <v>0.08629412742264796</v>
       </c>
       <c r="AC13">
-        <v>-0.05406359442077587</v>
+        <v>-0.08629412742264796</v>
       </c>
       <c r="AD13">
-        <v>2112.4</v>
+        <v>247.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>2112.4</v>
+        <v>247.5</v>
       </c>
       <c r="AG13">
-        <v>526</v>
+        <v>209.4</v>
       </c>
       <c r="AH13">
-        <v>0.7800590841949778</v>
+        <v>0.6897993311036789</v>
       </c>
       <c r="AI13">
-        <v>0.4117337491472566</v>
+        <v>0.4947031780931441</v>
       </c>
       <c r="AJ13">
-        <v>0.4689728958630528</v>
+        <v>0.6529466791393826</v>
       </c>
       <c r="AK13">
-        <v>0.1484156767585565</v>
+        <v>0.4530506274340112</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/research/traditional_assets/database/data/philippines/philippines_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09970000000000001</v>
+        <v>0.0885</v>
       </c>
       <c r="E2">
-        <v>0.112</v>
+        <v>0.136</v>
       </c>
       <c r="F2">
-        <v>0.229</v>
+        <v>0.12</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3295.6</v>
+        <v>4176</v>
       </c>
       <c r="L2">
-        <v>0.3012706828777768</v>
+        <v>0.3087615526802218</v>
       </c>
       <c r="M2">
-        <v>473.1995</v>
+        <v>879.6973</v>
       </c>
       <c r="N2">
-        <v>0.01463020962156814</v>
+        <v>0.02487817659402379</v>
       </c>
       <c r="O2">
-        <v>0.1435852348585993</v>
+        <v>0.2106554837164751</v>
       </c>
       <c r="P2">
-        <v>472.1755</v>
+        <v>879.3362999999999</v>
       </c>
       <c r="Q2">
-        <v>0.01459854996289884</v>
+        <v>0.02486796737575014</v>
       </c>
       <c r="R2">
-        <v>0.1432745175385362</v>
+        <v>0.2105690373563218</v>
       </c>
       <c r="S2">
-        <v>1.023999999999993</v>
+        <v>0.3610000000000033</v>
       </c>
       <c r="T2">
-        <v>0.002163992142848826</v>
+        <v>0.0004103684301406897</v>
       </c>
       <c r="U2">
-        <v>11209.7</v>
+        <v>9662.699999999999</v>
       </c>
       <c r="V2">
-        <v>0.3465774177590898</v>
+        <v>0.2732648570992245</v>
       </c>
       <c r="W2">
-        <v>0.09389561975768872</v>
+        <v>0.1077922241340246</v>
       </c>
       <c r="X2">
-        <v>0.1108490215241899</v>
+        <v>0.09577157378124272</v>
       </c>
       <c r="Y2">
-        <v>-0.01695340176650117</v>
+        <v>0.01202065035278189</v>
       </c>
       <c r="Z2">
-        <v>0.3028182471260987</v>
+        <v>0.349620604128377</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08158214459267932</v>
+        <v>0.06970591991294772</v>
       </c>
       <c r="AC2">
-        <v>-0.08158214459267932</v>
+        <v>-0.06970591991294772</v>
       </c>
       <c r="AD2">
-        <v>19453.5</v>
+        <v>18945.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19453.5</v>
+        <v>18945.1</v>
       </c>
       <c r="AG2">
-        <v>8243.799999999999</v>
+        <v>9282.4</v>
       </c>
       <c r="AH2">
-        <v>0.3755683189343115</v>
+        <v>0.3488628181779679</v>
       </c>
       <c r="AI2">
-        <v>0.3803322469583783</v>
+        <v>0.3360222062592563</v>
       </c>
       <c r="AJ2">
-        <v>0.2031102942263439</v>
+        <v>0.2079269576592761</v>
       </c>
       <c r="AK2">
-        <v>0.2064097749067328</v>
+        <v>0.1986908630115288</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0224</v>
+        <v>0.0116</v>
       </c>
       <c r="E3">
-        <v>-0.0225</v>
+        <v>-0.165</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>0.2534562211981567</v>
+        <v>0.1558441558441558</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>62.6</v>
+        <v>43.5</v>
       </c>
       <c r="V3">
-        <v>0.02929066067752199</v>
+        <v>0.02008217533816537</v>
       </c>
       <c r="W3">
-        <v>0.03280318091451292</v>
+        <v>0.03541912632821723</v>
       </c>
       <c r="X3">
-        <v>0.07958488326285784</v>
+        <v>0.06786884769647322</v>
       </c>
       <c r="Y3">
-        <v>-0.04678170234834492</v>
+        <v>-0.03244972136825599</v>
       </c>
       <c r="Z3">
-        <v>0.1460623737940319</v>
+        <v>0.278783490224475</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07958488326285784</v>
+        <v>0.06786884769647322</v>
       </c>
       <c r="AC3">
-        <v>-0.07958488326285784</v>
+        <v>-0.06786884769647322</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-62.6</v>
+        <v>-43.5</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03017449146823484</v>
+        <v>-0.02049373409968906</v>
       </c>
       <c r="AK3">
-        <v>-0.2266473569876901</v>
+        <v>-0.1327838827838828</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,14 +832,14 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="E4">
+        <v>0.194</v>
+      </c>
+      <c r="F4">
         <v>0.13</v>
       </c>
-      <c r="F4">
-        <v>0.173</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -853,28 +853,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>857.6</v>
+        <v>1253.4</v>
       </c>
       <c r="L4">
-        <v>0.2608510508866381</v>
+        <v>0.2958085528178986</v>
       </c>
       <c r="M4">
-        <v>86.59999999999999</v>
+        <v>231.8008</v>
       </c>
       <c r="N4">
-        <v>0.008665979525872851</v>
+        <v>0.01867839904593839</v>
       </c>
       <c r="O4">
-        <v>0.1009794776119403</v>
+        <v>0.1849376097016116</v>
       </c>
       <c r="P4">
-        <v>86.59999999999999</v>
+        <v>231.8008</v>
       </c>
       <c r="Q4">
-        <v>0.008665979525872851</v>
+        <v>0.01867839904593839</v>
       </c>
       <c r="R4">
-        <v>0.1009794776119403</v>
+        <v>0.1849376097016116</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2885.9</v>
+        <v>2965.7</v>
       </c>
       <c r="V4">
-        <v>0.2887892645925689</v>
+        <v>0.2389747060861717</v>
       </c>
       <c r="W4">
-        <v>0.1053976993412644</v>
+        <v>0.168200971577337</v>
       </c>
       <c r="X4">
-        <v>0.08912962585951779</v>
+        <v>0.07352721375792137</v>
       </c>
       <c r="Y4">
-        <v>0.01626807348174658</v>
+        <v>0.09467375781941564</v>
       </c>
       <c r="Z4">
-        <v>0.3945681916374633</v>
+        <v>0.545201883733498</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08052461958388121</v>
+        <v>0.0685431670161456</v>
       </c>
       <c r="AC4">
-        <v>-0.08052461958388121</v>
+        <v>-0.0685431670161456</v>
       </c>
       <c r="AD4">
-        <v>3118.2</v>
+        <v>3220.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3118.2</v>
+        <v>3220.9</v>
       </c>
       <c r="AG4">
-        <v>232.2999999999997</v>
+        <v>255.2000000000003</v>
       </c>
       <c r="AH4">
-        <v>0.23782538726137</v>
+        <v>0.2060584735461583</v>
       </c>
       <c r="AI4">
-        <v>0.2916467914363478</v>
+        <v>0.2661680852822081</v>
       </c>
       <c r="AJ4">
-        <v>0.02271793768458933</v>
+        <v>0.02014954245063285</v>
       </c>
       <c r="AK4">
-        <v>0.02975992210920082</v>
+        <v>0.02793559051153222</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>East West Banking Corporation (PSE:EW)</t>
+          <t>Metropolitan Bank &amp; Trust Company (PSE:MBT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +957,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00106</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="E5">
-        <v>-0.126</v>
+        <v>0.136</v>
+      </c>
+      <c r="F5">
+        <v>0.12</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,85 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>41.7</v>
+        <v>726.5</v>
       </c>
       <c r="L5">
-        <v>0.1223591549295775</v>
+        <v>0.3393749708039427</v>
       </c>
       <c r="M5">
-        <v>15.3</v>
+        <v>127.688</v>
       </c>
       <c r="N5">
-        <v>0.05677179962894249</v>
+        <v>0.03066842800528401</v>
       </c>
       <c r="O5">
-        <v>0.3669064748201439</v>
+        <v>0.1757577426015141</v>
       </c>
       <c r="P5">
-        <v>15.3</v>
+        <v>127.6</v>
       </c>
       <c r="Q5">
-        <v>0.05677179962894249</v>
+        <v>0.03064729194187582</v>
       </c>
       <c r="R5">
-        <v>0.3669064748201439</v>
+        <v>0.1756366139022711</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.08799999999999386</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.0006891798759475743</v>
       </c>
       <c r="U5">
-        <v>250.1</v>
+        <v>1933.8</v>
       </c>
       <c r="V5">
-        <v>0.9280148423005565</v>
+        <v>0.4644649933949802</v>
       </c>
       <c r="W5">
-        <v>0.03578477645241569</v>
+        <v>0.1380758704576555</v>
       </c>
       <c r="X5">
-        <v>0.09502109139944967</v>
+        <v>0.08257991183454308</v>
       </c>
       <c r="Y5">
-        <v>-0.05923631494703398</v>
+        <v>0.05549595862311238</v>
       </c>
       <c r="Z5">
-        <v>1.109375</v>
+        <v>0.3017535451495588</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08091012727303552</v>
+        <v>0.06918733291564329</v>
       </c>
       <c r="AC5">
-        <v>-0.08091012727303552</v>
+        <v>-0.06918733291564329</v>
       </c>
       <c r="AD5">
-        <v>136</v>
+        <v>2809.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>136</v>
+        <v>2809.4</v>
       </c>
       <c r="AG5">
-        <v>-114.1</v>
+        <v>875.6000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.3353884093711467</v>
+        <v>0.4029026660356523</v>
       </c>
       <c r="AI5">
-        <v>0.1179838639715451</v>
+        <v>0.3111357218007642</v>
       </c>
       <c r="AJ5">
-        <v>-0.7342342342342342</v>
+        <v>0.1737611875136433</v>
       </c>
       <c r="AK5">
-        <v>-0.1264125858630623</v>
+        <v>0.1233986780726355</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,13 +1082,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0852</v>
+        <v>0.13</v>
       </c>
       <c r="E6">
-        <v>0.112</v>
+        <v>0.163</v>
       </c>
       <c r="F6">
-        <v>0.226</v>
+        <v>0.104</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1103,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>629.4</v>
+        <v>842.2</v>
       </c>
       <c r="L6">
-        <v>0.3592670814544209</v>
+        <v>0.3745941377929992</v>
       </c>
       <c r="M6">
-        <v>150.7</v>
+        <v>232.3</v>
       </c>
       <c r="N6">
-        <v>0.01822756026464433</v>
+        <v>0.02507069006453841</v>
       </c>
       <c r="O6">
-        <v>0.2394343819510645</v>
+        <v>0.2758252196627879</v>
       </c>
       <c r="P6">
-        <v>150.7</v>
+        <v>232.3</v>
       </c>
       <c r="Q6">
-        <v>0.01822756026464433</v>
+        <v>0.02507069006453841</v>
       </c>
       <c r="R6">
-        <v>0.2394343819510645</v>
+        <v>0.2758252196627879</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>500.8</v>
+        <v>559.7</v>
       </c>
       <c r="V6">
-        <v>0.06057307352709943</v>
+        <v>0.06040492995747804</v>
       </c>
       <c r="W6">
-        <v>0.110152435289382</v>
+        <v>0.1577862709832134</v>
       </c>
       <c r="X6">
-        <v>0.08577202360543895</v>
+        <v>0.07237514967052987</v>
       </c>
       <c r="Y6">
-        <v>0.02438041168394309</v>
+        <v>0.08541112131268357</v>
       </c>
       <c r="Z6">
-        <v>0.2466735190999846</v>
+        <v>0.34540873546266</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08146098362522193</v>
+        <v>0.06934742215434653</v>
       </c>
       <c r="AC6">
-        <v>-0.08146098362522193</v>
+        <v>-0.06934742215434653</v>
       </c>
       <c r="AD6">
-        <v>1672.3</v>
+        <v>1915.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1672.3</v>
+        <v>1915.2</v>
       </c>
       <c r="AG6">
-        <v>1171.5</v>
+        <v>1355.5</v>
       </c>
       <c r="AH6">
-        <v>0.1682394366197183</v>
+        <v>0.1712905822377247</v>
       </c>
       <c r="AI6">
-        <v>0.237397612253879</v>
+        <v>0.2356473164849767</v>
       </c>
       <c r="AJ6">
-        <v>0.1241100940757691</v>
+        <v>0.127620912694303</v>
       </c>
       <c r="AK6">
-        <v>0.1790326277985787</v>
+        <v>0.1791165083182473</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Union Bank of the Philippines (PSE:UBP)</t>
+          <t>China Banking Corporation (PSE:CHIB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,10 +1207,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.135</v>
+        <v>0.203</v>
       </c>
       <c r="E7">
-        <v>0.0732</v>
+        <v>0.228</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,85 +1225,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>201.5</v>
+        <v>364</v>
       </c>
       <c r="L7">
-        <v>0.2798611111111111</v>
+        <v>0.4035029375900676</v>
       </c>
       <c r="M7">
-        <v>73.639</v>
+        <v>90.3</v>
       </c>
       <c r="N7">
-        <v>0.02223064150943396</v>
+        <v>0.06025221858944418</v>
       </c>
       <c r="O7">
-        <v>0.365454094292804</v>
+        <v>0.2480769230769231</v>
       </c>
       <c r="P7">
-        <v>72.7</v>
+        <v>90.3</v>
       </c>
       <c r="Q7">
-        <v>0.02194716981132076</v>
+        <v>0.06025221858944418</v>
       </c>
       <c r="R7">
-        <v>0.3607940446650124</v>
+        <v>0.2480769230769231</v>
       </c>
       <c r="S7">
-        <v>0.938999999999993</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.01275139532041436</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>747.7</v>
+        <v>704.8</v>
       </c>
       <c r="V7">
-        <v>0.2257207547169811</v>
+        <v>0.4702742376726496</v>
       </c>
       <c r="W7">
-        <v>0.09389561975768872</v>
+        <v>0.1613189150859776</v>
       </c>
       <c r="X7">
-        <v>0.1091466900830964</v>
+        <v>0.0931879556312058</v>
       </c>
       <c r="Y7">
-        <v>-0.01525107032540765</v>
+        <v>0.06813095945477185</v>
       </c>
       <c r="Z7">
-        <v>0.2803301666407101</v>
+        <v>0.3021806853582554</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08152684091429033</v>
+        <v>0.06962722224200441</v>
       </c>
       <c r="AC7">
-        <v>-0.08152684091429033</v>
+        <v>-0.06962722224200441</v>
       </c>
       <c r="AD7">
-        <v>3201.3</v>
+        <v>1740.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3201.3</v>
+        <v>1740.5</v>
       </c>
       <c r="AG7">
-        <v>2453.6</v>
+        <v>1035.7</v>
       </c>
       <c r="AH7">
-        <v>0.4914642758451288</v>
+        <v>0.5373240306248457</v>
       </c>
       <c r="AI7">
-        <v>0.5633413694194661</v>
+        <v>0.4107374631268437</v>
       </c>
       <c r="AJ7">
-        <v>0.4255215830457328</v>
+        <v>0.4086568813131313</v>
       </c>
       <c r="AK7">
-        <v>0.4971833839918947</v>
+        <v>0.2931751917796587</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1320,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Security Bank Corporation (PSE:SECB)</t>
+          <t>Union Bank of the Philippines (PSE:UBP)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,13 +1329,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.09970000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="E8">
-        <v>0.0269</v>
+        <v>0.0535</v>
       </c>
       <c r="F8">
-        <v>0.314</v>
+        <v>0.137</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,85 +1350,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>181.2</v>
+        <v>185.8</v>
       </c>
       <c r="L8">
-        <v>0.296078431372549</v>
+        <v>0.1809152872444012</v>
       </c>
       <c r="M8">
-        <v>38.4285</v>
+        <v>83.23700000000001</v>
       </c>
       <c r="N8">
-        <v>0.03263844063190079</v>
+        <v>0.030637882803298</v>
       </c>
       <c r="O8">
-        <v>0.2120778145695364</v>
+        <v>0.4479924650161464</v>
       </c>
       <c r="P8">
-        <v>38.4285</v>
+        <v>83.2</v>
       </c>
       <c r="Q8">
-        <v>0.03263844063190079</v>
+        <v>0.03062426383981154</v>
       </c>
       <c r="R8">
-        <v>0.2120778145695364</v>
+        <v>0.4477933261571582</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.03700000000000614</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.0004445138580199447</v>
       </c>
       <c r="U8">
-        <v>945</v>
+        <v>666.3</v>
       </c>
       <c r="V8">
-        <v>0.802615933412604</v>
+        <v>0.2452517667844523</v>
       </c>
       <c r="W8">
-        <v>0.07421059098169308</v>
+        <v>0.07530193726189512</v>
       </c>
       <c r="X8">
-        <v>0.1108490215241899</v>
+        <v>0.09568503220682134</v>
       </c>
       <c r="Y8">
-        <v>-0.03663843054249681</v>
+        <v>-0.02038309494492622</v>
       </c>
       <c r="Z8">
-        <v>0.4309373591707977</v>
+        <v>0.2648408891639589</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08158214459267932</v>
+        <v>0.06970342071124565</v>
       </c>
       <c r="AC8">
-        <v>-0.08158214459267932</v>
+        <v>-0.06970342071124565</v>
       </c>
       <c r="AD8">
-        <v>1203.4</v>
+        <v>3466.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1203.4</v>
+        <v>3466.3</v>
       </c>
       <c r="AG8">
-        <v>258.4000000000001</v>
+        <v>2800</v>
       </c>
       <c r="AH8">
-        <v>0.5054603494623656</v>
+        <v>0.560608756125568</v>
       </c>
       <c r="AI8">
-        <v>0.3623607347184583</v>
+        <v>0.5305101088170925</v>
       </c>
       <c r="AJ8">
-        <v>0.1799693550633794</v>
+        <v>0.5075406032482599</v>
       </c>
       <c r="AK8">
-        <v>0.1087542087542088</v>
+        <v>0.4771968095984729</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1442,7 +1445,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Metropolitan Bank &amp; Trust Company (PSE:MBT)</t>
+          <t>East West Banking Corporation (PSE:EW)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1451,13 +1454,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0568</v>
+        <v>0.0498</v>
       </c>
       <c r="E9">
-        <v>0.09519999999999999</v>
-      </c>
-      <c r="F9">
-        <v>0.232</v>
+        <v>0.0713</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1472,85 +1472,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>501.9</v>
+        <v>114</v>
       </c>
       <c r="L9">
-        <v>0.2954612350621063</v>
+        <v>0.2372034956304619</v>
       </c>
       <c r="M9">
-        <v>0.732</v>
+        <v>16.3</v>
       </c>
       <c r="N9">
-        <v>0.0001678706570347437</v>
+        <v>0.04710982658959538</v>
       </c>
       <c r="O9">
-        <v>0.0014584578601315</v>
+        <v>0.1429824561403509</v>
       </c>
       <c r="P9">
-        <v>0.647</v>
+        <v>16.3</v>
       </c>
       <c r="Q9">
-        <v>0.0001483774796468295</v>
+        <v>0.04710982658959538</v>
       </c>
       <c r="R9">
-        <v>0.001289101414624427</v>
+        <v>0.1429824561403509</v>
       </c>
       <c r="S9">
-        <v>0.08499999999999996</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.1161202185792349</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2540.6</v>
+        <v>232</v>
       </c>
       <c r="V9">
-        <v>0.5826396055498222</v>
+        <v>0.6705202312138728</v>
       </c>
       <c r="W9">
-        <v>0.08082255752910675</v>
+        <v>0.1121274712304515</v>
       </c>
       <c r="X9">
-        <v>0.1108834580227293</v>
+        <v>0.0958581153556641</v>
       </c>
       <c r="Y9">
-        <v>-0.03006090049362257</v>
+        <v>0.01626935587478735</v>
       </c>
       <c r="Z9">
-        <v>0.2607447657641063</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.08158323193629555</v>
+        <v>0.06970841911464978</v>
       </c>
       <c r="AC9">
-        <v>-0.08158323193629555</v>
+        <v>-0.06970841911464978</v>
       </c>
       <c r="AD9">
-        <v>4461.7</v>
+        <v>444.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>4461.7</v>
+        <v>444.2</v>
       </c>
       <c r="AG9">
-        <v>1921.1</v>
+        <v>212.2</v>
       </c>
       <c r="AH9">
-        <v>0.5057355308199768</v>
+        <v>0.5621361680587192</v>
       </c>
       <c r="AI9">
-        <v>0.4513560813749988</v>
+        <v>0.2792832442628104</v>
       </c>
       <c r="AJ9">
-        <v>0.3058297249108507</v>
+        <v>0.3801504836975994</v>
       </c>
       <c r="AK9">
-        <v>0.261569882224794</v>
+        <v>0.1562016930437983</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>China Banking Corporation (PSE:CHIB)</t>
+          <t>Bank of Commerce (PSE:BNCOM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1575,12 +1575,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.136</v>
-      </c>
-      <c r="E10">
-        <v>0.206</v>
-      </c>
       <c r="G10">
         <v>0</v>
       </c>
@@ -1594,85 +1588,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>316.8</v>
+        <v>41</v>
       </c>
       <c r="L10">
-        <v>0.4155299055613851</v>
+        <v>0.2543424317617866</v>
       </c>
       <c r="M10">
-        <v>68.8</v>
+        <v>0.024</v>
       </c>
       <c r="N10">
-        <v>0.05185408501658124</v>
+        <v>0.0001303639326453015</v>
       </c>
       <c r="O10">
-        <v>0.2171717171717172</v>
+        <v>0.0005853658536585366</v>
       </c>
       <c r="P10">
-        <v>68.8</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.05185408501658124</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.2171717171717172</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>1296</v>
+        <v>154.5</v>
       </c>
       <c r="V10">
-        <v>0.9767862526379258</v>
+        <v>0.8392178164041282</v>
       </c>
       <c r="W10">
-        <v>0.1420054686449415</v>
+        <v>0.1034569770375978</v>
       </c>
       <c r="X10">
-        <v>0.1265975456552416</v>
+        <v>0.09594689137721928</v>
       </c>
       <c r="Y10">
-        <v>0.0154079229896999</v>
+        <v>0.007510085660378502</v>
       </c>
       <c r="Z10">
-        <v>0.3019525525763396</v>
+        <v>0.3368861024033438</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.08197871439629928</v>
+        <v>0.06971096938500385</v>
       </c>
       <c r="AC10">
-        <v>-0.08197871439629928</v>
+        <v>-0.06971096938500385</v>
       </c>
       <c r="AD10">
-        <v>2039.2</v>
+        <v>237.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2039.2</v>
+        <v>237.1</v>
       </c>
       <c r="AG10">
-        <v>743.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AH10">
-        <v>0.6058229352347</v>
+        <v>0.5629154795821463</v>
       </c>
       <c r="AI10">
-        <v>0.4746078294465391</v>
+        <v>0.310543549443353</v>
       </c>
       <c r="AJ10">
-        <v>0.3590338164251208</v>
+        <v>0.3097112860892388</v>
       </c>
       <c r="AK10">
-        <v>0.2476837965740185</v>
+        <v>0.135632183908046</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1689,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rizal Commercial Banking Corporation (PSE:RCB)</t>
+          <t>Security Bank Corporation (PSE:SECB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1698,10 +1692,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.117</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="E11">
-        <v>0.256</v>
+        <v>0.0031</v>
+      </c>
+      <c r="F11">
+        <v>0.0542</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1716,28 +1713,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="L11">
-        <v>0.3106646058732612</v>
+        <v>0.2532214563979622</v>
       </c>
       <c r="M11">
-        <v>39</v>
+        <v>39.9355</v>
       </c>
       <c r="N11">
-        <v>0.04496713939813213</v>
+        <v>0.04106055932551923</v>
       </c>
       <c r="O11">
-        <v>0.1940298507462687</v>
+        <v>0.2363047337278106</v>
       </c>
       <c r="P11">
-        <v>39</v>
+        <v>39.9355</v>
       </c>
       <c r="Q11">
-        <v>0.04496713939813213</v>
+        <v>0.04106055932551923</v>
       </c>
       <c r="R11">
-        <v>0.1940298507462687</v>
+        <v>0.2363047337278106</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1746,55 +1743,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>777.4</v>
+        <v>422.8</v>
       </c>
       <c r="V11">
-        <v>0.8963449786694339</v>
+        <v>0.4347110836931935</v>
       </c>
       <c r="W11">
-        <v>0.09368445583780005</v>
+        <v>0.0798714495013942</v>
       </c>
       <c r="X11">
-        <v>0.1508420418103137</v>
+        <v>0.1051037820800417</v>
       </c>
       <c r="Y11">
-        <v>-0.05715758597251366</v>
+        <v>-0.02523233257864753</v>
       </c>
       <c r="Z11">
-        <v>0.191498360720756</v>
+        <v>0.2825930473811238</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.08234948825012406</v>
+        <v>0.0699328234866796</v>
       </c>
       <c r="AC11">
-        <v>-0.08234948825012406</v>
+        <v>-0.0699328234866796</v>
       </c>
       <c r="AD11">
-        <v>2020.4</v>
+        <v>1661.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2020.4</v>
+        <v>1661.1</v>
       </c>
       <c r="AG11">
-        <v>1243</v>
+        <v>1238.3</v>
       </c>
       <c r="AH11">
-        <v>0.6996571666031791</v>
+        <v>0.6307096480236929</v>
       </c>
       <c r="AI11">
-        <v>0.5062897809853155</v>
+        <v>0.4149948784570415</v>
       </c>
       <c r="AJ11">
-        <v>0.5890157797469554</v>
+        <v>0.5600886516803112</v>
       </c>
       <c r="AK11">
-        <v>0.3868417776671231</v>
+        <v>0.3459035168580128</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1820,10 +1817,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.169</v>
+        <v>0.0381</v>
       </c>
       <c r="E12">
-        <v>0.254</v>
+        <v>0.0428</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1838,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>318.4</v>
+        <v>242.8</v>
       </c>
       <c r="L12">
-        <v>0.3293679528292128</v>
+        <v>0.2979872361315661</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1865,55 +1862,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1165.5</v>
+        <v>1203.4</v>
       </c>
       <c r="V12">
-        <v>2.238333013251392</v>
+        <v>2.361923454367027</v>
       </c>
       <c r="W12">
-        <v>0.1077568701773386</v>
+        <v>0.08583448227100789</v>
       </c>
       <c r="X12">
-        <v>0.1590966071388105</v>
+        <v>0.1110827279055041</v>
       </c>
       <c r="Y12">
-        <v>-0.05133973696147197</v>
+        <v>-0.02524824563449619</v>
       </c>
       <c r="Z12">
-        <v>0.3003199850880735</v>
+        <v>0.2883635334088335</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.08243846375066191</v>
+        <v>0.07004395844491032</v>
       </c>
       <c r="AC12">
-        <v>-0.08243846375066191</v>
+        <v>-0.07004395844491032</v>
       </c>
       <c r="AD12">
-        <v>1353.5</v>
+        <v>1009.9</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1353.5</v>
+        <v>1009.9</v>
       </c>
       <c r="AG12">
-        <v>188</v>
+        <v>-193.5000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.7221747945790203</v>
+        <v>0.6646702645781228</v>
       </c>
       <c r="AI12">
-        <v>0.3188532120898019</v>
+        <v>0.2350408452998813</v>
       </c>
       <c r="AJ12">
-        <v>0.2652744461690419</v>
+        <v>-0.6123417721518993</v>
       </c>
       <c r="AK12">
-        <v>0.0610508540624797</v>
+        <v>-0.06255455338958398</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1930,114 +1927,236 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Rizal Commercial Banking Corporation (PSE:RCB)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="E13">
+        <v>0.219</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>195.3</v>
+      </c>
+      <c r="L13">
+        <v>0.2919282511210762</v>
+      </c>
+      <c r="M13">
+        <v>58.112</v>
+      </c>
+      <c r="N13">
+        <v>0.0578516674962668</v>
+      </c>
+      <c r="O13">
+        <v>0.297552483358935</v>
+      </c>
+      <c r="P13">
+        <v>57.9</v>
+      </c>
+      <c r="Q13">
+        <v>0.05764061722249875</v>
+      </c>
+      <c r="R13">
+        <v>0.2964669738863287</v>
+      </c>
+      <c r="S13">
+        <v>0.2120000000000033</v>
+      </c>
+      <c r="T13">
+        <v>0.003648127753304021</v>
+      </c>
+      <c r="U13">
+        <v>734.3</v>
+      </c>
+      <c r="V13">
+        <v>0.7310104529616724</v>
+      </c>
+      <c r="W13">
+        <v>0.09913705583756345</v>
+      </c>
+      <c r="X13">
+        <v>0.1151335786287353</v>
+      </c>
+      <c r="Y13">
+        <v>-0.01599652279117185</v>
+      </c>
+      <c r="Z13">
+        <v>0.2086848456433997</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.07010832004312445</v>
+      </c>
+      <c r="AC13">
+        <v>-0.07010832004312445</v>
+      </c>
+      <c r="AD13">
+        <v>2177.7</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>2177.7</v>
+      </c>
+      <c r="AG13">
+        <v>1443.4</v>
+      </c>
+      <c r="AH13">
+        <v>0.6843378794544654</v>
+      </c>
+      <c r="AI13">
+        <v>0.4566844919786096</v>
+      </c>
+      <c r="AJ13">
+        <v>0.5896482699456678</v>
+      </c>
+      <c r="AK13">
+        <v>0.3577908879083833</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Philippine Bank of Communications (PSE:PBC)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.0645</v>
-      </c>
-      <c r="E13">
-        <v>0.198</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>29.6</v>
-      </c>
-      <c r="L13">
-        <v>0.3414071510957324</v>
-      </c>
-      <c r="M13">
+      <c r="D14">
+        <v>0.0885</v>
+      </c>
+      <c r="E14">
+        <v>0.31</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>30</v>
+      </c>
+      <c r="L14">
+        <v>0.3009027081243731</v>
+      </c>
+      <c r="M14">
         <v>-0</v>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>-0</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>-0</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>-0</v>
       </c>
-      <c r="Q13">
+      <c r="Q14">
         <v>-0</v>
       </c>
-      <c r="R13">
+      <c r="R14">
         <v>-0</v>
       </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>38.1</v>
-      </c>
-      <c r="V13">
-        <v>0.3423180592991914</v>
-      </c>
-      <c r="W13">
-        <v>0.1125047510452299</v>
-      </c>
-      <c r="X13">
-        <v>0.1476054938259125</v>
-      </c>
-      <c r="Y13">
-        <v>-0.03510074278068259</v>
-      </c>
-      <c r="Z13">
-        <v>0.2789575289575289</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.08629412742264796</v>
-      </c>
-      <c r="AC13">
-        <v>-0.08629412742264796</v>
-      </c>
-      <c r="AD13">
-        <v>247.5</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>247.5</v>
-      </c>
-      <c r="AG13">
-        <v>209.4</v>
-      </c>
-      <c r="AH13">
-        <v>0.6897993311036789</v>
-      </c>
-      <c r="AI13">
-        <v>0.4947031780931441</v>
-      </c>
-      <c r="AJ13">
-        <v>0.6529466791393826</v>
-      </c>
-      <c r="AK13">
-        <v>0.4530506274340112</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>41.9</v>
+      </c>
+      <c r="V14">
+        <v>0.3420408163265306</v>
+      </c>
+      <c r="W14">
+        <v>0.1186708860759494</v>
+      </c>
+      <c r="X14">
+        <v>0.1146400303983089</v>
+      </c>
+      <c r="Y14">
+        <v>0.004030855677640457</v>
+      </c>
+      <c r="Z14">
+        <v>0.2157074859368239</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.07307401049893822</v>
+      </c>
+      <c r="AC14">
+        <v>-0.07307401049893822</v>
+      </c>
+      <c r="AD14">
+        <v>262.8</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>262.8</v>
+      </c>
+      <c r="AG14">
+        <v>220.9</v>
+      </c>
+      <c r="AH14">
+        <v>0.6820659226576694</v>
+      </c>
+      <c r="AI14">
+        <v>0.4707989967753493</v>
+      </c>
+      <c r="AJ14">
+        <v>0.6432731508444963</v>
+      </c>
+      <c r="AK14">
+        <v>0.4278520240170444</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/philippines/philippines_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.129</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="E2">
-        <v>0.168</v>
+        <v>0.123</v>
       </c>
       <c r="F2">
-        <v>0.112</v>
+        <v>0.141</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1089.4</v>
+        <v>4830.9</v>
       </c>
       <c r="L2">
-        <v>0.3874248728617661</v>
+        <v>0.3094905568510878</v>
       </c>
       <c r="M2">
-        <v>333.94</v>
+        <v>1127.15</v>
       </c>
       <c r="N2">
-        <v>0.03015395728926814</v>
+        <v>0.02803479134643605</v>
       </c>
       <c r="O2">
-        <v>0.3065357077290251</v>
+        <v>0.2333209132873792</v>
       </c>
       <c r="P2">
-        <v>327.3</v>
+        <v>1116.14</v>
       </c>
       <c r="Q2">
-        <v>0.02955438168766084</v>
+        <v>0.0277609475344108</v>
       </c>
       <c r="R2">
-        <v>0.3004406095098219</v>
+        <v>0.231041834854789</v>
       </c>
       <c r="S2">
-        <v>6.639999999999986</v>
+        <v>11.00999999999999</v>
       </c>
       <c r="T2">
-        <v>0.01988381146313705</v>
+        <v>0.009767998935367955</v>
       </c>
       <c r="U2">
-        <v>605.4</v>
+        <v>11752.5</v>
       </c>
       <c r="V2">
-        <v>0.05466612488148449</v>
+        <v>0.2923114805473891</v>
       </c>
       <c r="W2">
-        <v>0.1763981994235565</v>
+        <v>0.1094826834162087</v>
       </c>
       <c r="X2">
-        <v>0.07824454200167516</v>
+        <v>0.09850233858959981</v>
       </c>
       <c r="Y2">
-        <v>0.09815365742188131</v>
+        <v>0.01098034482660887</v>
       </c>
       <c r="Z2">
-        <v>0.3733618366019147</v>
+        <v>0.350020572891282</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07367159414652111</v>
+        <v>0.07311122967862824</v>
       </c>
       <c r="AC2">
-        <v>-0.07367159414652111</v>
+        <v>-0.07311122967862824</v>
       </c>
       <c r="AD2">
-        <v>2939.5</v>
+        <v>28864.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2939.5</v>
+        <v>28864.8</v>
       </c>
       <c r="AG2">
-        <v>2334.1</v>
+        <v>17112.3</v>
       </c>
       <c r="AH2">
-        <v>0.2097545311831026</v>
+        <v>0.4179052616034122</v>
       </c>
       <c r="AI2">
-        <v>0.2743888209541768</v>
+        <v>0.4034123625467494</v>
       </c>
       <c r="AJ2">
-        <v>0.1740748474859418</v>
+        <v>0.298551756263772</v>
       </c>
       <c r="AK2">
-        <v>0.2309275290625773</v>
+        <v>0.2861631696798112</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,120 +704,1340 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Philippine Trust Company (PSE:PTC)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.09939999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.192</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>14</v>
+      </c>
+      <c r="L3">
+        <v>0.1645123384253819</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>42.9</v>
+      </c>
+      <c r="V3">
+        <v>0.02093806432719996</v>
+      </c>
+      <c r="W3">
+        <v>0.0377256804095931</v>
+      </c>
+      <c r="X3">
+        <v>0.07285193209744684</v>
+      </c>
+      <c r="Y3">
+        <v>-0.03512625168785374</v>
+      </c>
+      <c r="Z3">
+        <v>0.2597680097680097</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.07285193209744684</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07285193209744684</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-42.9</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.02138584247258225</v>
+      </c>
+      <c r="AK3">
+        <v>-0.1160086533261222</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BDO Unibank, Inc. (PSE:BDO)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.102</v>
+      </c>
+      <c r="E4">
+        <v>0.131</v>
+      </c>
+      <c r="F4">
+        <v>0.128</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1429.8</v>
+      </c>
+      <c r="L4">
+        <v>0.2932562146197391</v>
+      </c>
+      <c r="M4">
+        <v>281.9</v>
+      </c>
+      <c r="N4">
+        <v>0.02156534245213014</v>
+      </c>
+      <c r="O4">
+        <v>0.1971604420198629</v>
+      </c>
+      <c r="P4">
+        <v>281.9</v>
+      </c>
+      <c r="Q4">
+        <v>0.02156534245213014</v>
+      </c>
+      <c r="R4">
+        <v>0.1971604420198629</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>3686.5</v>
+      </c>
+      <c r="V4">
+        <v>0.2820171512939971</v>
+      </c>
+      <c r="W4">
+        <v>0.1637519326576189</v>
+      </c>
+      <c r="X4">
+        <v>0.08010801858194204</v>
+      </c>
+      <c r="Y4">
+        <v>0.08364391407567691</v>
+      </c>
+      <c r="Z4">
+        <v>0.5360217240734836</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.07296524047468919</v>
+      </c>
+      <c r="AC4">
+        <v>-0.07296524047468919</v>
+      </c>
+      <c r="AD4">
+        <v>4675</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>4675</v>
+      </c>
+      <c r="AG4">
+        <v>988.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.263426288534899</v>
+      </c>
+      <c r="AI4">
+        <v>0.3148169347941737</v>
+      </c>
+      <c r="AJ4">
+        <v>0.07030383203891781</v>
+      </c>
+      <c r="AK4">
+        <v>0.08854829173907591</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Philippine National Bank (PSE:PNB)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0742</v>
+      </c>
+      <c r="E5">
+        <v>0.184</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>346.4</v>
+      </c>
+      <c r="L5">
+        <v>0.3601580370139322</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1227.7</v>
+      </c>
+      <c r="V5">
+        <v>1.687096330905593</v>
+      </c>
+      <c r="W5">
+        <v>0.1074508344190086</v>
+      </c>
+      <c r="X5">
+        <v>0.08228126090948117</v>
+      </c>
+      <c r="Y5">
+        <v>0.02516957350952745</v>
+      </c>
+      <c r="Z5">
+        <v>0.339606652307475</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07298840927984064</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07298840927984064</v>
+      </c>
+      <c r="AD5">
+        <v>338.2</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>338.2</v>
+      </c>
+      <c r="AG5">
+        <v>-889.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.3172905525846702</v>
+      </c>
+      <c r="AI5">
+        <v>0.08275018350868607</v>
+      </c>
+      <c r="AJ5">
+        <v>5.497527812113722</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3110901269541496</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>China Banking Corporation (PSE:CBC)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.133</v>
+      </c>
+      <c r="E6">
+        <v>0.212</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>431.8</v>
+      </c>
+      <c r="L6">
+        <v>0.4141569154037982</v>
+      </c>
+      <c r="M6">
+        <v>105.7</v>
+      </c>
+      <c r="N6">
+        <v>0.03592061442261946</v>
+      </c>
+      <c r="O6">
+        <v>0.2447892542843909</v>
+      </c>
+      <c r="P6">
+        <v>105.7</v>
+      </c>
+      <c r="Q6">
+        <v>0.03592061442261946</v>
+      </c>
+      <c r="R6">
+        <v>0.2447892542843909</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1067.4</v>
+      </c>
+      <c r="V6">
+        <v>0.362740433630123</v>
+      </c>
+      <c r="W6">
+        <v>0.1730453252113974</v>
+      </c>
+      <c r="X6">
+        <v>0.08611773037672901</v>
+      </c>
+      <c r="Y6">
+        <v>0.08692759483466841</v>
+      </c>
+      <c r="Z6">
+        <v>0.2965132813833115</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.07302198432399416</v>
+      </c>
+      <c r="AC6">
+        <v>-0.07302198432399416</v>
+      </c>
+      <c r="AD6">
+        <v>1924</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1924</v>
+      </c>
+      <c r="AG6">
+        <v>856.5999999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.3953478814778285</v>
+      </c>
+      <c r="AI6">
+        <v>0.3985252081693525</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2254685196883554</v>
+      </c>
+      <c r="AK6">
+        <v>0.2277949154345282</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bank of Commerce (PSE:BNCOM)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>53.6</v>
+      </c>
+      <c r="L7">
+        <v>0.2816605359957961</v>
+      </c>
+      <c r="M7">
+        <v>11.7</v>
+      </c>
+      <c r="N7">
+        <v>0.07173513182096873</v>
+      </c>
+      <c r="O7">
+        <v>0.2182835820895522</v>
+      </c>
+      <c r="P7">
+        <v>11.7</v>
+      </c>
+      <c r="Q7">
+        <v>0.07173513182096873</v>
+      </c>
+      <c r="R7">
+        <v>0.2182835820895522</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>200.5</v>
+      </c>
+      <c r="V7">
+        <v>1.229307173513182</v>
+      </c>
+      <c r="W7">
+        <v>0.1183745583038869</v>
+      </c>
+      <c r="X7">
+        <v>0.09850233858959981</v>
+      </c>
+      <c r="Y7">
+        <v>0.01987221971428711</v>
+      </c>
+      <c r="Z7">
+        <v>0.3124794745484401</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.07309209850398558</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07309209850398558</v>
+      </c>
+      <c r="AD7">
+        <v>206.2</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>206.2</v>
+      </c>
+      <c r="AG7">
+        <v>5.699999999999989</v>
+      </c>
+      <c r="AH7">
+        <v>0.5583536420254536</v>
+      </c>
+      <c r="AI7">
+        <v>0.2607486090035407</v>
+      </c>
+      <c r="AJ7">
+        <v>0.03376777251184828</v>
+      </c>
+      <c r="AK7">
+        <v>0.009656107064204623</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>East West Banking Corporation (PSE:EW)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0566</v>
+      </c>
+      <c r="E8">
+        <v>0.0358</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>125.5</v>
+      </c>
+      <c r="L8">
+        <v>0.2187554470977863</v>
+      </c>
+      <c r="M8">
+        <v>21.7</v>
+      </c>
+      <c r="N8">
+        <v>0.05686582809224318</v>
+      </c>
+      <c r="O8">
+        <v>0.1729083665338645</v>
+      </c>
+      <c r="P8">
+        <v>21.7</v>
+      </c>
+      <c r="Q8">
+        <v>0.05686582809224318</v>
+      </c>
+      <c r="R8">
+        <v>0.1729083665338645</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>240.6</v>
+      </c>
+      <c r="V8">
+        <v>0.630503144654088</v>
+      </c>
+      <c r="W8">
+        <v>0.1094826834162087</v>
+      </c>
+      <c r="X8">
+        <v>0.1036468988247291</v>
+      </c>
+      <c r="Y8">
+        <v>0.005835784591479612</v>
+      </c>
+      <c r="Z8">
+        <v>0.422304011777696</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.07311122967862824</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07311122967862824</v>
+      </c>
+      <c r="AD8">
+        <v>579.2</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>579.2</v>
+      </c>
+      <c r="AG8">
+        <v>338.6</v>
+      </c>
+      <c r="AH8">
+        <v>0.6028309741881765</v>
+      </c>
+      <c r="AI8">
+        <v>0.309484370825541</v>
+      </c>
+      <c r="AJ8">
+        <v>0.4701471813385171</v>
+      </c>
+      <c r="AK8">
+        <v>0.2076154270648108</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Metropolitan Bank &amp; Trust Company (PSE:MBT)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0819</v>
+      </c>
+      <c r="E9">
+        <v>0.115</v>
+      </c>
+      <c r="F9">
+        <v>0.141</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>824.1</v>
+      </c>
+      <c r="L9">
+        <v>0.3349591513230094</v>
+      </c>
+      <c r="M9">
+        <v>245.27</v>
+      </c>
+      <c r="N9">
+        <v>0.04399146249596442</v>
+      </c>
+      <c r="O9">
+        <v>0.2976216478582696</v>
+      </c>
+      <c r="P9">
+        <v>240.9</v>
+      </c>
+      <c r="Q9">
+        <v>0.04320766223051261</v>
+      </c>
+      <c r="R9">
+        <v>0.2923188933381871</v>
+      </c>
+      <c r="S9">
+        <v>4.370000000000005</v>
+      </c>
+      <c r="T9">
+        <v>0.0178170995229747</v>
+      </c>
+      <c r="U9">
+        <v>1936.7</v>
+      </c>
+      <c r="V9">
+        <v>0.3473652114646483</v>
+      </c>
+      <c r="W9">
+        <v>0.1363297986732618</v>
+      </c>
+      <c r="X9">
+        <v>0.1079323743902775</v>
+      </c>
+      <c r="Y9">
+        <v>0.02839742428298432</v>
+      </c>
+      <c r="Z9">
+        <v>0.3602881954105467</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.07312445199523104</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07312445199523104</v>
+      </c>
+      <c r="AD9">
+        <v>9640.1</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>9640.1</v>
+      </c>
+      <c r="AG9">
+        <v>7703.400000000001</v>
+      </c>
+      <c r="AH9">
+        <v>0.6335710295422431</v>
+      </c>
+      <c r="AI9">
+        <v>0.5802535272307027</v>
+      </c>
+      <c r="AJ9">
+        <v>0.5801277223845529</v>
+      </c>
+      <c r="AK9">
+        <v>0.5248656051345992</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Security Bank Corporation (PSE:SECB)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.092</v>
+      </c>
+      <c r="E10">
+        <v>0.004670000000000001</v>
+      </c>
+      <c r="F10">
+        <v>0.247</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>178.4</v>
+      </c>
+      <c r="L10">
+        <v>0.2239517951292995</v>
+      </c>
+      <c r="M10">
+        <v>40.689</v>
+      </c>
+      <c r="N10">
+        <v>0.03604624379872431</v>
+      </c>
+      <c r="O10">
+        <v>0.2280773542600897</v>
+      </c>
+      <c r="P10">
+        <v>40.689</v>
+      </c>
+      <c r="Q10">
+        <v>0.03604624379872431</v>
+      </c>
+      <c r="R10">
+        <v>0.2280773542600897</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1139.1</v>
+      </c>
+      <c r="V10">
+        <v>1.009124734231042</v>
+      </c>
+      <c r="W10">
+        <v>0.07624257446899441</v>
+      </c>
+      <c r="X10">
+        <v>0.1151786916405086</v>
+      </c>
+      <c r="Y10">
+        <v>-0.03893611717151421</v>
+      </c>
+      <c r="Z10">
+        <v>0.223445822943168</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.07314269207583665</v>
+      </c>
+      <c r="AC10">
+        <v>-0.07314269207583665</v>
+      </c>
+      <c r="AD10">
+        <v>2354.9</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>2354.9</v>
+      </c>
+      <c r="AG10">
+        <v>1215.8</v>
+      </c>
+      <c r="AH10">
+        <v>0.6759766914487471</v>
+      </c>
+      <c r="AI10">
+        <v>0.4794763203974428</v>
+      </c>
+      <c r="AJ10">
+        <v>0.5185532713469249</v>
+      </c>
+      <c r="AK10">
+        <v>0.3222967420406649</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Union Bank of the Philippines (PSE:UBP)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.142</v>
+      </c>
+      <c r="E11">
+        <v>0.00342</v>
+      </c>
+      <c r="F11">
+        <v>0.31</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>170.1</v>
+      </c>
+      <c r="L11">
+        <v>0.1660322108345534</v>
+      </c>
+      <c r="M11">
+        <v>42.7</v>
+      </c>
+      <c r="N11">
+        <v>0.02077151335311573</v>
+      </c>
+      <c r="O11">
+        <v>0.2510288065843622</v>
+      </c>
+      <c r="P11">
+        <v>42.7</v>
+      </c>
+      <c r="Q11">
+        <v>0.02077151335311573</v>
+      </c>
+      <c r="R11">
+        <v>0.2510288065843622</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>899.7</v>
+      </c>
+      <c r="V11">
+        <v>0.4376611373254853</v>
+      </c>
+      <c r="W11">
+        <v>0.0556464276367443</v>
+      </c>
+      <c r="X11">
+        <v>0.1169187359678646</v>
+      </c>
+      <c r="Y11">
+        <v>-0.06127230833112029</v>
+      </c>
+      <c r="Z11">
+        <v>0.2089537018152152</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.07314646043331975</v>
+      </c>
+      <c r="AC11">
+        <v>-0.07314646043331975</v>
+      </c>
+      <c r="AD11">
+        <v>4464.9</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>4464.9</v>
+      </c>
+      <c r="AG11">
+        <v>3565.2</v>
+      </c>
+      <c r="AH11">
+        <v>0.684737600834279</v>
+      </c>
+      <c r="AI11">
+        <v>0.5644627054361567</v>
+      </c>
+      <c r="AJ11">
+        <v>0.6342756498069704</v>
+      </c>
+      <c r="AK11">
+        <v>0.5085659672196625</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Bank of the Philippine Islands (PSE:BPI)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D12">
         <v>0.129</v>
       </c>
-      <c r="E3">
+      <c r="E12">
         <v>0.168</v>
       </c>
-      <c r="F3">
+      <c r="F12">
         <v>0.112</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>1089.4</v>
       </c>
-      <c r="L3">
+      <c r="L12">
         <v>0.3874248728617661</v>
       </c>
-      <c r="M3">
+      <c r="M12">
         <v>333.94</v>
       </c>
-      <c r="N3">
+      <c r="N12">
         <v>0.03015395728926814</v>
       </c>
-      <c r="O3">
+      <c r="O12">
         <v>0.3065357077290251</v>
       </c>
-      <c r="P3">
+      <c r="P12">
         <v>327.3</v>
       </c>
-      <c r="Q3">
+      <c r="Q12">
         <v>0.02955438168766084</v>
       </c>
-      <c r="R3">
+      <c r="R12">
         <v>0.3004406095098219</v>
       </c>
-      <c r="S3">
+      <c r="S12">
         <v>6.639999999999986</v>
       </c>
-      <c r="T3">
+      <c r="T12">
         <v>0.01988381146313705</v>
       </c>
-      <c r="U3">
+      <c r="U12">
         <v>605.4</v>
       </c>
-      <c r="V3">
+      <c r="V12">
         <v>0.05466612488148449</v>
       </c>
-      <c r="W3">
+      <c r="W12">
         <v>0.1763981994235565</v>
       </c>
-      <c r="X3">
-        <v>0.07824454200167516</v>
-      </c>
-      <c r="Y3">
-        <v>0.09815365742188131</v>
-      </c>
-      <c r="Z3">
+      <c r="X12">
+        <v>0.07823721954160537</v>
+      </c>
+      <c r="Y12">
+        <v>0.0981609798819511</v>
+      </c>
+      <c r="Z12">
         <v>0.3733618366019147</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.07367159414652111</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07367159414652111</v>
-      </c>
-      <c r="AD3">
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.07366580760563035</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07366580760563035</v>
+      </c>
+      <c r="AD12">
         <v>2939.5</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
         <v>2939.5</v>
       </c>
-      <c r="AG3">
+      <c r="AG12">
         <v>2334.1</v>
       </c>
-      <c r="AH3">
+      <c r="AH12">
         <v>0.2097545311831026</v>
       </c>
-      <c r="AI3">
+      <c r="AI12">
         <v>0.2743888209541768</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ12">
         <v>0.1740748474859418</v>
       </c>
-      <c r="AK3">
+      <c r="AK12">
         <v>0.2309275290625773</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rizal Commercial Banking Corporation (PSE:RCB)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0867</v>
+      </c>
+      <c r="E13">
+        <v>0.108</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>167.8</v>
+      </c>
+      <c r="L13">
+        <v>0.2132689374682258</v>
+      </c>
+      <c r="M13">
+        <v>43.55099999999999</v>
+      </c>
+      <c r="N13">
+        <v>0.04207013137557959</v>
+      </c>
+      <c r="O13">
+        <v>0.2595411203814064</v>
+      </c>
+      <c r="P13">
+        <v>43.55099999999999</v>
+      </c>
+      <c r="Q13">
+        <v>0.04207013137557959</v>
+      </c>
+      <c r="R13">
+        <v>0.2595411203814064</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>706</v>
+      </c>
+      <c r="V13">
+        <v>0.6819938176197836</v>
+      </c>
+      <c r="W13">
+        <v>0.06477263954296303</v>
+      </c>
+      <c r="X13">
+        <v>0.1070091775037188</v>
+      </c>
+      <c r="Y13">
+        <v>-0.04223653796075577</v>
+      </c>
+      <c r="Z13">
+        <v>0.1953461049828898</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.07594488963536514</v>
+      </c>
+      <c r="AC13">
+        <v>-0.07594488963536514</v>
+      </c>
+      <c r="AD13">
+        <v>1742.8</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1742.8</v>
+      </c>
+      <c r="AG13">
+        <v>1036.8</v>
+      </c>
+      <c r="AH13">
+        <v>0.6273578113750899</v>
+      </c>
+      <c r="AI13">
+        <v>0.3818580192813322</v>
+      </c>
+      <c r="AJ13">
+        <v>0.5003861003861003</v>
+      </c>
+      <c r="AK13">
+        <v>0.2687402799377916</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
         <v>0</v>
       </c>
     </row>
